--- a/day3.xlsx
+++ b/day3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92D63FC-9415-A541-A6E1-7A1F3C495AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5B9EE2-D171-2345-8A51-704BCABD5540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{95BF2A7D-BC62-9B4A-A2D5-026FC9DBC691}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="agenda" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -355,10 +355,10 @@
   <numFmts count="6">
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;#,##0.00_);[Red]\(&quot;₹&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="&quot;₹&quot;#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="174" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="175" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -439,16 +439,7 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -457,19 +448,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -547,8 +547,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>93080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -567,7 +567,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -1005,106 +1005,106 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="5" t="str">
+      <c r="B11" s="2" t="str">
         <f>"+"</f>
         <v>+</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B12" s="5" t="str">
+      <c r="B12" s="2" t="str">
         <f>"-"</f>
         <v>-</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="5" t="str">
+      <c r="B13" s="2" t="str">
         <f>"*"</f>
         <v>*</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B14" s="5" t="str">
+      <c r="B14" s="2" t="str">
         <f>"/"</f>
         <v>/</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="5" t="str">
+      <c r="B15" s="2" t="str">
         <f>"^"</f>
         <v>^</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
@@ -1112,7 +1112,7 @@
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E24" s="6"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F25" t="s">
@@ -1123,166 +1123,166 @@
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7" t="s">
+      <c r="G29" s="4"/>
+      <c r="H29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7" t="s">
+      <c r="G31" s="4"/>
+      <c r="H31" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8">
+      <c r="G33" s="4"/>
+      <c r="H33" s="5">
         <v>-10</v>
       </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="8">
+      <c r="G35" s="4"/>
+      <c r="H35" s="5">
         <v>-10</v>
       </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7" t="s">
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="14">
+      <c r="G38" s="4"/>
+      <c r="H38" s="11">
         <v>46072</v>
       </c>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="15">
+      <c r="G40" s="4"/>
+      <c r="H40" s="12">
         <v>46072</v>
       </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="9">
+      <c r="G42" s="4"/>
+      <c r="H42" s="6">
         <v>0.89236111111111116</v>
       </c>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7" t="s">
+      <c r="G44" s="4"/>
+      <c r="H44" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7" t="s">
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
@@ -1290,11 +1290,11 @@
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
@@ -1332,70 +1332,70 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="5" t="str">
+      <c r="B4" s="2" t="str">
         <f>"+"</f>
         <v>+</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="2" t="str">
         <f>"-"</f>
         <v>-</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="5" t="str">
+      <c r="B6" s="2" t="str">
         <f>"*"</f>
         <v>*</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="5" t="str">
+      <c r="B7" s="2" t="str">
         <f>"/"</f>
         <v>/</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="5" t="str">
+      <c r="B8" s="2" t="str">
         <f>"^"</f>
         <v>^</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1422,61 +1422,61 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="2">
         <f>C16+C17</f>
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="2">
         <f>C16-C17</f>
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="2">
         <f>C16*C17</f>
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="2">
         <f>C16/C17</f>
         <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="2">
         <f>C16^C17</f>
         <v>512</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
@@ -1484,7 +1484,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D32" s="10"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -1503,37 +1503,37 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8">
+      <c r="C43" s="4"/>
+      <c r="D43" s="5">
         <v>-10</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8">
+      <c r="C45" s="4"/>
+      <c r="D45" s="5">
         <v>-10</v>
       </c>
     </row>
@@ -1546,26 +1546,26 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C50" s="11">
+      <c r="C50" s="8">
         <v>0</v>
       </c>
-      <c r="E50" s="12">
+      <c r="E50" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C51" s="11">
+      <c r="C51" s="8">
         <v>90</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="9">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C52" s="11">
+      <c r="C52" s="8">
         <v>999999</v>
       </c>
-      <c r="E52" s="12">
+      <c r="E52" s="9">
         <v>999999</v>
       </c>
     </row>
@@ -1581,43 +1581,43 @@
       <c r="C58">
         <v>10000000</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="8">
         <v>10000000</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="8">
         <f>2*D58</f>
         <v>20000000</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="14">
+      <c r="D64" s="4"/>
+      <c r="E64" s="11">
         <v>46072</v>
       </c>
     </row>
     <row r="65" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
     </row>
     <row r="66" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="15">
+      <c r="D66" s="4"/>
+      <c r="E66" s="12">
         <v>46072</v>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
     </row>
     <row r="73" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C73" s="16"/>
+      <c r="C73" s="13"/>
     </row>
     <row r="74" spans="3:6" x14ac:dyDescent="0.2">
       <c r="D74" t="s">
@@ -1641,19 +1641,19 @@
       <c r="C76">
         <v>1</v>
       </c>
-      <c r="D76" s="18">
+      <c r="D76" s="15">
         <v>1</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="10">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="77" spans="3:6" x14ac:dyDescent="0.2">
       <c r="C77">
         <v>2</v>
       </c>
-      <c r="D77" s="18">
+      <c r="D77" s="15">
         <v>2</v>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       <c r="C78">
         <v>3</v>
       </c>
-      <c r="D78" s="18">
+      <c r="D78" s="15">
         <v>3</v>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       <c r="C79">
         <v>4</v>
       </c>
-      <c r="D79" s="18">
+      <c r="D79" s="15">
         <v>4</v>
       </c>
     </row>
@@ -1677,17 +1677,17 @@
       <c r="C80">
         <v>5</v>
       </c>
-      <c r="D80" s="18">
+      <c r="D80" s="15">
         <v>5</v>
       </c>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C81">
         <v>6</v>
       </c>
-      <c r="D81" s="18">
+      <c r="D81" s="15">
         <v>6</v>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       <c r="C82">
         <v>7</v>
       </c>
-      <c r="D82" s="18">
+      <c r="D82" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
@@ -1719,29 +1719,29 @@
       <c r="C92">
         <v>0.56699999999999995</v>
       </c>
-      <c r="D92" s="19">
+      <c r="D92" s="16">
         <v>0.56699999999999995</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C100">
         <v>0.05</v>
       </c>
-      <c r="E100" s="20">
+      <c r="E100" s="17">
         <v>0.05</v>
       </c>
       <c r="F100" t="s">
@@ -1766,19 +1766,19 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E109" s="20">
+      <c r="E109" s="17">
         <v>378098000</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
@@ -1801,7 +1801,7 @@
       <c r="D120" t="s">
         <v>59</v>
       </c>
-      <c r="E120" s="21" t="s">
+      <c r="E120" s="18" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="D121" t="s">
         <v>64</v>
       </c>
-      <c r="E121" s="21" t="s">
+      <c r="E121" s="18" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       <c r="D122" t="s">
         <v>65</v>
       </c>
-      <c r="E122" s="21" t="s">
+      <c r="E122" s="18" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       <c r="D123" t="s">
         <v>66</v>
       </c>
-      <c r="E123" s="21" t="s">
+      <c r="E123" s="18" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1851,21 +1851,21 @@
       <c r="D124" t="s">
         <v>67</v>
       </c>
-      <c r="E124" s="21" t="s">
+      <c r="E124" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E125" s="21"/>
+      <c r="E125" s="18"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
@@ -1930,13 +1930,13 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3"/>
-      <c r="G148" s="3"/>
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B151" t="s">
@@ -2016,24 +2016,24 @@
       </c>
     </row>
     <row r="169" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B169" s="23" t="s">
+      <c r="B169" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C169" s="23" t="s">
+      <c r="C169" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="D169" s="23" t="s">
+      <c r="D169" s="20" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="170" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B170" s="22" t="s">
+      <c r="B170" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C170" s="22">
+      <c r="C170" s="19">
         <v>4000</v>
       </c>
-      <c r="D170" s="22">
+      <c r="D170" s="19">
         <v>17</v>
       </c>
       <c r="F170" t="s">
@@ -2041,24 +2041,24 @@
       </c>
     </row>
     <row r="171" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B171" s="22" t="s">
+      <c r="B171" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C171" s="22">
+      <c r="C171" s="19">
         <v>5600</v>
       </c>
-      <c r="D171" s="22">
+      <c r="D171" s="19">
         <v>18</v>
       </c>
     </row>
     <row r="172" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B172" s="22" t="s">
+      <c r="B172" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C172" s="22">
+      <c r="C172" s="19">
         <v>9700</v>
       </c>
-      <c r="D172" s="22">
+      <c r="D172" s="19">
         <v>19</v>
       </c>
       <c r="F172">
@@ -2071,24 +2071,24 @@
       </c>
     </row>
     <row r="173" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B173" s="22" t="s">
+      <c r="B173" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C173" s="22">
+      <c r="C173" s="19">
         <v>4000</v>
       </c>
-      <c r="D173" s="22">
+      <c r="D173" s="19">
         <v>20</v>
       </c>
     </row>
     <row r="174" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B174" s="22" t="s">
+      <c r="B174" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C174" s="22">
+      <c r="C174" s="19">
         <v>8000</v>
       </c>
-      <c r="D174" s="22">
+      <c r="D174" s="19">
         <v>21</v>
       </c>
       <c r="F174" t="s">
@@ -2096,24 +2096,24 @@
       </c>
     </row>
     <row r="175" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B175" s="22" t="s">
+      <c r="B175" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C175" s="22">
+      <c r="C175" s="19">
         <v>9000</v>
       </c>
-      <c r="D175" s="22">
+      <c r="D175" s="19">
         <v>17</v>
       </c>
     </row>
     <row r="176" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B176" s="22" t="s">
+      <c r="B176" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C176" s="22">
+      <c r="C176" s="19">
         <v>15000</v>
       </c>
-      <c r="D176" s="22">
+      <c r="D176" s="19">
         <v>18</v>
       </c>
       <c r="F176">
@@ -2126,35 +2126,35 @@
       </c>
     </row>
     <row r="177" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B177" s="22" t="s">
+      <c r="B177" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C177" s="22">
+      <c r="C177" s="19">
         <v>34000</v>
       </c>
-      <c r="D177" s="22">
+      <c r="D177" s="19">
         <v>16</v>
       </c>
     </row>
     <row r="178" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B178" s="22" t="s">
+      <c r="B178" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C178" s="22">
+      <c r="C178" s="19">
         <v>9000</v>
       </c>
-      <c r="D178" s="22">
+      <c r="D178" s="19">
         <v>20</v>
       </c>
     </row>
     <row r="179" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B179" s="22" t="s">
+      <c r="B179" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C179" s="22">
+      <c r="C179" s="19">
         <v>9000</v>
       </c>
-      <c r="D179" s="22">
+      <c r="D179" s="19">
         <v>24</v>
       </c>
       <c r="F179" t="s">

--- a/day3.xlsx
+++ b/day3.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8090A26-D289-DF40-86C3-BF4850C3BC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DD933C-C758-DD40-94BF-A53D07EED81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16660" xr2:uid="{46EC9735-D3C4-1F42-ABC2-96E23C5A8B91}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{46EC9735-D3C4-1F42-ABC2-96E23C5A8B91}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="agenda" sheetId="1" r:id="rId1"/>
+    <sheet name="data_type" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="BASIC_ARITH" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,8 +38,185 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+  <si>
+    <t>Fundamentals (3)</t>
+  </si>
+  <si>
+    <t>Arithmetic Op</t>
+  </si>
+  <si>
+    <t>Data types</t>
+  </si>
+  <si>
+    <t>Flash Fill</t>
+  </si>
+  <si>
+    <t>Quick Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrow + CTRL </t>
+  </si>
+  <si>
+    <t>NAVIGATION</t>
+  </si>
+  <si>
+    <t>ARROW+SHIFT+CTRL</t>
+  </si>
+  <si>
+    <t>SELECTION</t>
+  </si>
+  <si>
+    <t>CTRL + A</t>
+  </si>
+  <si>
+    <t>Entire data range selection</t>
+  </si>
+  <si>
+    <t>ARITHMETICS vs MATHEMATICS</t>
+  </si>
+  <si>
+    <t>Arthimetics</t>
+  </si>
+  <si>
+    <t>To evaluate a expression</t>
+  </si>
+  <si>
+    <t>we must begin that with = in the cell</t>
+  </si>
+  <si>
+    <t>BODMAS</t>
+  </si>
+  <si>
+    <t>Binary operator</t>
+  </si>
+  <si>
+    <t>bracket</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>div</t>
+  </si>
+  <si>
+    <t>mul</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>()</t>
+  </si>
+  <si>
+    <t>% or Mul</t>
+  </si>
+  <si>
+    <t>Divide</t>
+  </si>
+  <si>
+    <t>Mul</t>
+  </si>
+  <si>
+    <t>3+(3*2-(4*5))</t>
+  </si>
+  <si>
+    <t>3+(3*2-20)</t>
+  </si>
+  <si>
+    <t>3+(6-20)</t>
+  </si>
+  <si>
+    <t>3+(-14)</t>
+  </si>
+  <si>
+    <t>(-11)</t>
+  </si>
+  <si>
+    <t>Exponents</t>
+  </si>
+  <si>
+    <t>(Repeated Mult.)</t>
+  </si>
+  <si>
+    <t>DATA TYPE</t>
+  </si>
+  <si>
+    <t>NUMBER</t>
+  </si>
+  <si>
+    <t>CURRENCY vs ACCOUNTING</t>
+  </si>
+  <si>
+    <t>Spends (in INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT DATE </t>
+  </si>
+  <si>
+    <t>LONG DATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATES </t>
+  </si>
+  <si>
+    <t>no date is stored for formats</t>
+  </si>
+  <si>
+    <t>Formatting is fetched from local setting</t>
+  </si>
+  <si>
+    <t>ALL DATES are stored as a number In the backend</t>
+  </si>
+  <si>
+    <t>TIME</t>
+  </si>
+  <si>
+    <t>hh:mm:ss</t>
+  </si>
+  <si>
+    <t>24 hour format</t>
+  </si>
+  <si>
+    <t>12 hour format</t>
+  </si>
+  <si>
+    <t>DECIMALS</t>
+  </si>
+  <si>
+    <t>ALL TIME are decimals b/w 0 to 1 mapping 24 hrs of the day</t>
+  </si>
+  <si>
+    <t>4 Aug 2026 TIME 6PM</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>anything inside " "</t>
+  </si>
+  <si>
+    <t>any combination of characters is called text</t>
+  </si>
+  <si>
+    <t>char: *,s,e,A,s,;,',#</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="173" formatCode="[$-409]hh:mm:ss\ AM/PM;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -46,12 +226,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -66,8 +252,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -83,6 +293,623 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>146052</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>470535</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>162399</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34687D2A-C0AD-7461-A5B2-345BEF1582A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="473075" y="958852"/>
+          <a:ext cx="822960" cy="1641947"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>664880</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>94960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>213240</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>193440</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E343927-A8F3-63F0-711A-3E5B95E06F08}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2315880" y="1110960"/>
+            <a:ext cx="716760" cy="301680"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E343927-A8F3-63F0-711A-3E5B95E06F08}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2309760" y="1104840"/>
+              <a:ext cx="729000" cy="313920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>545000</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>16880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>494760</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>13120</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="11" name="Ink 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83AB2A00-56B7-D483-07AF-FFC5A5A5E731}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2196000" y="1439280"/>
+            <a:ext cx="1118160" cy="199440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="11" name="Ink 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83AB2A00-56B7-D483-07AF-FFC5A5A5E731}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2187000" y="1385280"/>
+              <a:ext cx="1135800" cy="307080"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>319640</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>96440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>475160</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>169360</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="12" name="Ink 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FE12EA4-F95F-5BD0-5313-6EBBB1C46003}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1970640" y="1518840"/>
+            <a:ext cx="155520" cy="276120"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="12" name="Ink 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FE12EA4-F95F-5BD0-5313-6EBBB1C46003}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1961640" y="1464840"/>
+              <a:ext cx="173160" cy="383760"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>620940</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>72880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>862140</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>159640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="15" name="Ink 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{455939D4-C6B8-A825-D414-3DC616559BBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3097440" y="1698480"/>
+            <a:ext cx="241200" cy="86760"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="Ink 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{455939D4-C6B8-A825-D414-3DC616559BBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3088440" y="1644480"/>
+              <a:ext cx="258840" cy="194400"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216340</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>124320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>305620</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>136760</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="18" name="Ink 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B647D0-67B2-6E53-BA89-94F35BBEACD7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1041840" y="1343520"/>
+            <a:ext cx="89280" cy="215640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="Ink 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B647D0-67B2-6E53-BA89-94F35BBEACD7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1035720" y="1337410"/>
+              <a:ext cx="101520" cy="227860"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>248740</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>36520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>293020</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>26640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="19" name="Ink 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3308FBCA-2288-6E4E-05BA-24D8D96C1FD1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1074240" y="1662120"/>
+            <a:ext cx="44280" cy="193320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="19" name="Ink 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3308FBCA-2288-6E4E-05BA-24D8D96C1FD1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1068120" y="1656000"/>
+              <a:ext cx="56520" cy="205560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:35:01.521"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">196 270 24575,'-1'8'0,"0"14"0,1 22 0,0 27 0,0 11 0,0-3 0,0-16 0,0-24 0,0-16 0,0-12 0,0-7 0,0-3 0,1-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1399">0 287 24575,'9'0'0,"6"0"0,11-2 0,4 0 0,3 1 0,0 0 0,-2 1 0,2 0 0,-3 2 0,1 4 0,-2 4 0,-2 4 0,-1 4 0,-1 4 0,-1 4 0,-1 3 0,-2 1 0,-3 0 0,-6-6 0,-4-4 0,-5-5 0,-4-2 0,-3 1 0,-5 2 0,-3 4 0,-6 7 0,-5 3 0,-4 2 0,-3 0 0,1-4 0,0-3 0,3-4 0,5-6 0,2-5 0,-1-2 0,-1-2 0,-3-1 0,0-1 0,2-2 0,3 0 0,6-1 0,5-1 0,3-1 0,-2 0 0,4 0 0,-2 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3982">998 508 24575,'-8'0'0,"-7"0"0,-6 0 0,-8 0 0,-3 0 0,-2 0 0,0 0 0,3 2 0,4 3 0,7 3 0,5 3 0,6-1 0,3 2 0,2 3 0,2 4 0,2 5 0,4 8 0,9 6 0,9 0 0,13-2 0,3-9 0,4-7 0,-2-8 0,-8-7 0,-6-5 0,-7-7 0,-3-7 0,0-10 0,1-8 0,-2-2 0,-2 2 0,-4 6 0,-5 7 0,-2 10 0,-3 4 0,-2 3 0,-2-2 0,0-3 0,-1-2 0,0-1 0,2 1 0,0-1 0,2 1 0,1 1 0,0 2 0,1 4 0,8 12 0,7 7 0,11 13 0,5 3 0,2 2 0,-2-3 0,-2-4 0,-6-8 0,-4-7 0,-4-6 0,-1-3 0,3-3 0,3-2 0,2-3 0,-1-4 0,-2-3 0,-4-8 0,-3-19 0,-5-24 0,-3-26 0,-3 37 0,-2-2 0,-1 0 0,-1 1 0,-8-43 0,-5 17 0,-2 19 0,2 16 0,3 15 0,3 10 0,3 9 0,2 6 0,2 2 0,1 3 0,1 3 0,0 4 0,0 8 0,3 16 0,4 19 0,8 27 0,-3-28 0,1 3 0,3 4 0,0 1 0,1-1 0,-1-3 0,15 39 0,-3-24 0,-6-26 0,-3-15 0,-6-15 0,-3-9 0,1-4 0,7 0 0,5-3 0,3-3 0,-1-1 0,-6-1 0,-8 2 0,-5 3 0,-3 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4765">1272 419 24575,'17'0'0,"12"0"0,14 0 0,5 0 0,-7 0 0,-12 0 0,-15 0 0,-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6699">1788 505 24575,'-5'0'0,"0"1"0,0 2 0,-2 3 0,-1 6 0,-1 5 0,0 5 0,2 3 0,2 3 0,3 1 0,1 3 0,2 0 0,3-1 0,6-3 0,6-7 0,5-7 0,0-7 0,-1-4 0,-4-3 0,-4-2 0,-4-1 0,-2-3 0,-1-3 0,1-3 0,0-3 0,2-5 0,0-5 0,1-6 0,-1-1 0,-1 0 0,-3 6 0,-1 7 0,-2 8 0,-1 6 0,-1 3 0,0 3 0,-1 3 0,0 4 0,0 3 0,-1 2 0,0 1 0,0 1 0,1 0 0,1 1 0,1 0 0,2-1 0,2-1 0,2-2 0,2-3 0,0-2 0,-1-2 0,0 0 0,1 0 0,0 0 0,0 0 0,-2-1 0,-1-1 0,-1-1 0,-2-2 0,0 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:36:13.935"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.3" units="cm"/>
+      <inkml:brushProperty name="color" value="#849398"/>
+      <inkml:brushProperty name="inkEffects" value="pencil"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1395 0 16383,'0'8'0,"0"4"0,0 5 0,0 3 0,0 2 0,0-2 0,0-1 0,0-2 0,0 0 0,0-2 0,-1-2 0,-1-2 0,0-4 0,0-2 0,-1-2 0,0-2 0,-1-1 0,-2 0 0,-9 0 0,-21 0 0,-35-1 0,20 0 0,-4 1 0,-13-1 0,-4 0 0,-6 0 0,-1 1 0,2 0 0,0 1 0,6 1 0,3 1 0,12 0 0,4 1 0,-35 8 0,19 0 0,9 0 0,4-2 0,9-2 0,5-3 0,8-2 0,7-2 0,10-1 0,6 0 0,7 1 0,1 0 0,3 1 0,-1 0 0,2 0 0,0 1 0,1 4 0,2 6 0,-1 7 0,2 6 0,-2 5 0,0 0 0,0-3 0,-2-6 0,-1-8 0,1-6 0,-1-5 0,0-4 0,0-5 0,-1 2 0,0-2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2650">1476 212 16383,'9'-4'0,"8"-3"0,11-5 0,18-4 0,17-2 0,9 1 0,3 4 0,-6 4 0,-8 5 0,-8 4 0,-6 0 0,-6 0 0,-5 0 0,-5 0 0,-1 0 0,-3 0 0,6 0 0,7 0 0,8 0 0,6 0 0,0 0 0,-2 0 0,-4 0 0,-4 0 0,-6 0 0,-1 0 0,-5 0 0,-5 0 0,-5 2 0,-5 1 0,-4 0 0,-4-1 0,-2 0 0,1 0 0,1 0 0,4 0 0,3 0 0,2 1 0,3 0 0,1 0 0,1 1 0,0 0 0,-2 0 0,-3 0 0,-2 0 0,-4-1 0,-2 0 0,-3 0 0,-1 0 0,0 1 0,-2 0 0,1 1 0,-1 5 0,1 6 0,1 11 0,2 8 0,1 7 0,2 5 0,-1 0 0,0-3 0,-2-6 0,-2-10 0,-2-10 0,-1-8 0,-1-5 0,0-4 0,0-4 0,-1 2 0,0-2 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:36:27.451"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.3" units="cm"/>
+      <inkml:brushProperty name="color" value="#849398"/>
+      <inkml:brushProperty name="inkEffects" value="pencil"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">19 473 16383,'1'18'0,"0"13"0,-1 16 0,0 8 0,0-3 0,0-12 0,0-13 0,0-12 0,0-8 0,0-6 0,0-11 0,0 1 0,-1-13 0,0-6 0,-1-17 0,-1-27 0,-1-20 0,1-5 0,-1 8 0,2 22 0,1 26 0,3 18 0,1 15 0,3 6 0,4 4 0,9 4 0,6 4 0,8 5 0,4 4 0,0 3 0,1 2 0,-4 0 0,-3-2 0,-4-1 0,-1-1 0,-2-1 0,-1-2 0,-3-2 0,-6-4 0,-4-3 0,-4-4 0,-3-3 0,-1-3 0,-1-6 0,-1-7 0,0-7 0,0-3 0,0-1 0,0 1 0,-1 1 0,-1-2 0,1-5 0,-1-4 0,1-2 0,-1 1 0,1 3 0,-1 6 0,0 5 0,1 8 0,-1 5 0,1 5 0,-3 5 0,2 0 0,0 2 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:36:33.001"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.3" units="cm"/>
+      <inkml:brushProperty name="color" value="#849398"/>
+      <inkml:brushProperty name="inkEffects" value="pencil"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">452 135 16383,'0'6'0,"0"1"0,0-1 0,0 3 0,0 1 0,0 3 0,0-1 0,0 0 0,0-3 0,0-2 0,0-1 0,0-2 0,0-1 0,1-2 0,-1-5 0,-4-8 0,-5-9 0,-2-7 0,0-2 0,3 2 0,4 6 0,2 6 0,2 7 0,0 4 0,4 3 0,2 1 0,5 1 0,3 1 0,2 5 0,0 6 0,1 6 0,1 2 0,2 0 0,3-3 0,3-1 0,1-3 0,-3-1 0,-5-3 0,-7-3 0,-5-3 0,-4-2 0,-1-2 0,-1-6 0,-1-7 0,0-9 0,0-6 0,0-3 0,0 3 0,0 5 0,0 6 0,0 6 0,-1 3 0,1 4 0,-2 0 0,1 2 0,0 1 0,0 0 0,-1 2 0,0-1 0,1 1 0,0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1567">0 219 16383,'0'-15'0,"0"0"0,1-1 0,2 3 0,1 2 0,3 5 0,1 4 0,1 1 0,-1 1 0,0 2 0,-1 3 0,-1 4 0,0 2 0,0-1 0,-1-1 0,0-3 0,0-3 0,1-1 0,-1-2 0,0 0 0,-1 0 0,-1-2 0,-2-2 0,-1-3 0,0-2 0,0-2 0,-2-2 0,-1 1 0,0 2 0,1 3 0,1 3 0,1 2 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:38:02.133"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 9 24575,'16'0'0,"2"0"0,4 0 0,1 0 0,-2 0 0,-4 0 0,-6 0 0,-4 0 0,-2 0 0,-1 0 0,-2 0 0,1 0 0,0 0 0,1 0 0,0-1 0,0 1 0,0-1 0,-1-1 0,0 0 0,-2 1 0,-1-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2467">12 219 24575,'7'-1'0,"2"0"0,6 1 0,1 0 0,3 0 0,-1 0 0,-2 0 0,-2 0 0,-3 0 0,-1 0 0,0 0 0,-1 0 0,2 0 0,-2 0 0,0 0 0,-3 0 0,-1 0 0,-1 0 0,-2 1 0,-1 1 0,-1 2 0,0 1 0,0 3 0,0 1 0,0 1 0,0 1 0,1 1 0,2 0 0,-1 2 0,1-1 0,-1 0 0,1 1 0,0 3 0,0 1 0,-1 1 0,0 2 0,-1-1 0,1-1 0,-1-2 0,0-1 0,0 0 0,0-2 0,0-2 0,0-1 0,0-2 0,0-2 0,-1-2 0,0-1 0,-1-1 0,-1-1 0,-2-1 0,-3 0 0,0 1 0,-1 0 0,1 0 0,-2 1 0,0-1 0,0 1 0,-1 0 0,0-1 0,1 0 0,0-1 0,0-1 0,1 0 0,0-1 0,1-1 0,0-1 0,1-1 0,0 1 0,1 2 0,1-1 0,0 2 0,1 0 0,0-1 0,1-2 0,1 1 0,2-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:38:07.250"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">32 6 24575,'10'0'0,"1"0"0,1 0 0,0 0 0,-2 0 0,-2 0 0,-4 0 0,-1-2 0,-1 0 0,-1 0 0,-1 2 0,0 2 0,-1 3 0,0 1 0,0 0 0,-1 3 0,0 1 0,0 4 0,1 2 0,1 4 0,0 1 0,0 1 0,0 1 0,0 1 0,1 1 0,1 1 0,2 1 0,-1 1 0,0-2 0,0 0 0,-1-3 0,-1-3 0,0-1 0,0-3 0,-1-2 0,0-3 0,0-1 0,0-2 0,0 0 0,1-1 0,-1-1 0,1 0 0,-1-1 0,1 1 0,0-1 0,-1 0 0,1-1 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 0 0,0-1 0,-1 0 0,-3-1 0,-1 0 0,-3-1 0,-2 0 0,-2-2 0,-1-1 0,0-1 0,1-1 0,2 3 0,2 0 0,2 2 0,2 0 0,0 0 0,1 0 0,1 0 0,0 0 0,0-1 0,0 0 0,2-2 0,0-2 0,1-3 0,-1 3 0,1 0 0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +1229,603 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF41FB1-49DC-3A40-AFA3-57CD558B7C2A}">
+  <dimension ref="A2:G40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2D4421-5602-7847-825B-E5B2B05208AD}">
+  <dimension ref="A2:E76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C14" s="4">
+        <v>646464</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C15" s="4">
+        <v>377373</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C16" s="4">
+        <v>38383.938999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C17" s="4">
+        <v>8383.8330000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C18" s="4">
+        <v>8383.3999000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="6">
+        <v>646464</v>
+      </c>
+      <c r="D25" s="8">
+        <v>646464</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="6">
+        <v>377373</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8">
+        <v>377373</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="6">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>38383.938999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="6">
+        <v>8383.8330000000005</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="6">
+        <v>-8383.3999000000003</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-8383.3999000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="10">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="11">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="10">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
+      <c r="C36" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>36728</v>
+      </c>
+      <c r="C43" s="10">
+        <v>36728</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B44" s="12">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
+      <c r="C44" s="10">
+        <f ca="1">TODAY()</f>
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="2"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+      <c r="C57" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>0.75</v>
+      </c>
+      <c r="C58" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>0.46929999999999999</v>
+      </c>
+      <c r="C59" s="15">
+        <v>0.46930555555555553</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="5">
+        <v>46238.75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B66" s="10"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B67" s="16">
+        <f ca="1">NOW()</f>
+        <v>46238.960435532405</v>
+      </c>
+      <c r="C67" s="4">
+        <f ca="1">NOW()</f>
+        <v>46238.960435532405</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C74" s="10"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76E6187-BB7D-FF45-85A7-991D881D0EA5}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC51D2CE-A6FB-1946-8382-119F0CDA3C1A}">
+  <dimension ref="A2:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="4" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" t="str">
+        <f>"+,-,*,/,^"</f>
+        <v>+,-,*,/,^</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <f>3+4*5-7</f>
+        <v>16</v>
+      </c>
+      <c r="C10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B10)</f>
+        <v>=3+4*5-7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22">
+        <f>3+(3*2-(4*5))</f>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
+      <c r="C31" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B31)</f>
+        <v>=2^3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <f>4^6</f>
+        <v>4096</v>
+      </c>
+      <c r="C33" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(B33)</f>
+        <v>=4^6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/day3.xlsx
+++ b/day3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DD933C-C758-DD40-94BF-A53D07EED81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC5A93A-B882-3C43-B297-12A9CB276331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{46EC9735-D3C4-1F42-ABC2-96E23C5A8B91}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>Fundamentals (3)</t>
   </si>
@@ -204,18 +204,61 @@
   </si>
   <si>
     <t>char: *,s,e,A,s,;,',#</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Scientific Notation</t>
+  </si>
+  <si>
+    <t>Fraction</t>
+  </si>
+  <si>
+    <t>PERCENTAGE</t>
+  </si>
+  <si>
+    <t>PER HUNDRED</t>
+  </si>
+  <si>
+    <t>SCIENTIFIC NOT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUMBERS that are too large or </t>
+  </si>
+  <si>
+    <t>too small to write</t>
+  </si>
+  <si>
+    <t>#.{…} * 10^{..}</t>
+  </si>
+  <si>
+    <t>5.0*10^-2</t>
+  </si>
+  <si>
+    <t>5/(10^2)</t>
+  </si>
+  <si>
+    <t>E --&gt; 10 raised to the power</t>
+  </si>
+  <si>
+    <t>FRACTION</t>
+  </si>
+  <si>
+    <t>P/Q</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="173" formatCode="[$-409]hh:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="[$-409]hh:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="169" formatCode="#\ ??/16"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -252,32 +295,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="13" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -296,6 +343,531 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>565200</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>24966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>690120</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>180486</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA8F0CA7-4C2A-94F6-CB3B-E437604C7E61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1390320" y="10302840"/>
+            <a:ext cx="124920" cy="155520"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA8F0CA7-4C2A-94F6-CB3B-E437604C7E61}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1384200" y="10296720"/>
+              <a:ext cx="137160" cy="167760"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>515520</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>56359</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738360</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>56719</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="3" name="Ink 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B51B29-BD39-2E67-F42C-35E35D8C3A17}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1340640" y="10535760"/>
+            <a:ext cx="222840" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="Ink 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1B51B29-BD39-2E67-F42C-35E35D8C3A17}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1334520" y="10529640"/>
+              <a:ext cx="235080" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>551448</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>47573</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>62928</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>146286</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="20" name="Ink 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03CAA024-4832-150A-B04C-EB50EF1E5BB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2825280" y="10123920"/>
+            <a:ext cx="336600" cy="300240"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="20" name="Ink 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03CAA024-4832-150A-B04C-EB50EF1E5BB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2819160" y="10117800"/>
+              <a:ext cx="348840" cy="312480"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1422720</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>1206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>365688</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>192366</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{127BA509-D43B-F613-F56B-1DFEE11C5005}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2247840" y="10279080"/>
+            <a:ext cx="391680" cy="191160"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{127BA509-D43B-F613-F56B-1DFEE11C5005}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2241714" y="10272960"/>
+              <a:ext cx="403931" cy="203400"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1060560</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>175086</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1227240</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>30079</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="22" name="Ink 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EAE61C7-3BA9-6135-916B-5604491765D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1885680" y="10452960"/>
+            <a:ext cx="166680" cy="56520"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="22" name="Ink 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EAE61C7-3BA9-6135-916B-5604491765D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1879547" y="10446840"/>
+              <a:ext cx="178946" cy="68760"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>478440</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>156439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>706680</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>166232</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="23" name="Ink 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B67B47-546B-6848-D78A-23FF907539D3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1303560" y="10635840"/>
+            <a:ext cx="228240" cy="211320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="Ink 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B67B47-546B-6848-D78A-23FF907539D3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1297440" y="10629730"/>
+              <a:ext cx="240480" cy="223539"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>354528</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>93945</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>420048</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>193018</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="36" name="Ink 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EB61F04-7B67-DDDC-866C-3040C097E8C1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2628360" y="10976400"/>
+            <a:ext cx="890640" cy="300600"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="36" name="Ink 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EB61F04-7B67-DDDC-866C-3040C097E8C1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2622242" y="10970273"/>
+              <a:ext cx="902875" cy="312855"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>948240</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>191865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>78048</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>14604</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="38" name="Ink 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FB8F3AF-70D4-E2D1-3E5A-E05EEA221386}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1773360" y="11074320"/>
+            <a:ext cx="578520" cy="427320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="38" name="Ink 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FB8F3AF-70D4-E2D1-3E5A-E05EEA221386}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1767240" y="11068200"/>
+              <a:ext cx="590760" cy="439560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -354,8 +926,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>193440</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Ink 7">
@@ -374,7 +946,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Ink 7">
@@ -419,8 +991,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>13120</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="11" name="Ink 10">
@@ -439,7 +1011,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="11" name="Ink 10">
@@ -484,8 +1056,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>169360</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Ink 11">
@@ -504,7 +1076,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Ink 11">
@@ -549,8 +1121,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>159640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" Requires="xdr14 aink">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink">
+      <mc:Choice Requires="xdr14 aink">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -569,7 +1141,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -614,8 +1186,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>136760</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Ink 17">
@@ -634,7 +1206,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Ink 17">
@@ -679,8 +1251,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>26640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="19" name="Ink 18">
@@ -699,7 +1271,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="19" name="Ink 18">
@@ -721,6 +1293,786 @@
             <a:xfrm>
               <a:off x="1068120" y="1656000"/>
               <a:ext cx="56520" cy="205560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1313940</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>186720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1426980</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>193560</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="3" name="Ink 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEEC8E59-0D20-0A15-3DFB-E615A4C93ECF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="4476240" y="17255520"/>
+            <a:ext cx="113040" cy="6840"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="Ink 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEEC8E59-0D20-0A15-3DFB-E615A4C93ECF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4470120" y="17249400"/>
+              <a:ext cx="125280" cy="19080"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>668820</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>165840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>989580</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>41480</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="4" name="Ink 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2114ED0F-FE43-9C47-2598-23A61F767A72}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3831120" y="17234640"/>
+            <a:ext cx="320760" cy="78840"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="Ink 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2114ED0F-FE43-9C47-2598-23A61F767A72}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3825000" y="17228520"/>
+              <a:ext cx="333000" cy="91080"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444580</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>202440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>594340</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>44960</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="Ink 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA1DCF4F-9E70-FC81-E8A8-18BB6CD23475}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1270080" y="17880840"/>
+            <a:ext cx="149760" cy="45720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="Ink 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA1DCF4F-9E70-FC81-E8A8-18BB6CD23475}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1263960" y="17874720"/>
+              <a:ext cx="162000" cy="57960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219380</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>540500</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>7120</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="6" name="Ink 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BF24AE4-2BEB-1126-9BA6-C85CE79FF2A5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2213280" y="17282160"/>
+            <a:ext cx="321120" cy="200160"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="Ink 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BF24AE4-2BEB-1126-9BA6-C85CE79FF2A5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2207160" y="17276040"/>
+              <a:ext cx="333360" cy="212400"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>445460</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>186000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1138620</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>140680</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="7" name="Ink 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B1AE8F5-B1A7-F890-91E7-80FFFA9136D3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2439360" y="17254800"/>
+            <a:ext cx="1861560" cy="361080"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="7" name="Ink 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B1AE8F5-B1A7-F890-91E7-80FFFA9136D3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2433240" y="17248680"/>
+              <a:ext cx="1873800" cy="373320"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1230060</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>48120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>30560</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>41120</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="9" name="Ink 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD782847-D8CE-BBA9-14B9-3DAC82FF3C68}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="4392360" y="17116920"/>
+            <a:ext cx="261000" cy="196200"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="Ink 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD782847-D8CE-BBA9-14B9-3DAC82FF3C68}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4386240" y="17110800"/>
+              <a:ext cx="273240" cy="208440"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>770540</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>146160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>771980</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>187760</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="10" name="Ink 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81773B7C-146E-2BBA-A9A7-0CCEB9505935}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2764440" y="18434160"/>
+            <a:ext cx="1440" cy="244800"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="10" name="Ink 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81773B7C-146E-2BBA-A9A7-0CCEB9505935}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2758320" y="18428040"/>
+              <a:ext cx="13680" cy="257040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>149340</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>60680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>909660</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>9040</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="27" name="Ink 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5969D82B-AFE7-B51A-C772-BE63F993DB17}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3311640" y="18551880"/>
+            <a:ext cx="760320" cy="151560"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="27" name="Ink 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5969D82B-AFE7-B51A-C772-BE63F993DB17}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3305517" y="18545745"/>
+              <a:ext cx="772566" cy="163829"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1084980</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>153720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1365420</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>176960</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="31" name="Ink 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC89BF12-C2E0-3B08-FC7B-38321F34D41E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="4247280" y="18441720"/>
+            <a:ext cx="280440" cy="226440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="31" name="Ink 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC89BF12-C2E0-3B08-FC7B-38321F34D41E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4241160" y="18435590"/>
+              <a:ext cx="292680" cy="238699"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1002020</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>157360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1002380</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>157720</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="32" name="Ink 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C28873D-206F-CF08-32F2-C0275D11F51C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2995920" y="18851760"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="32" name="Ink 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C28873D-206F-CF08-32F2-C0275D11F51C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2987280" y="18842760"/>
+              <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>145020</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>1120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38480</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>23640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="43" name="Ink 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0079343-68BE-2AC7-9F01-7F7A827009FB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3307320" y="18695520"/>
+            <a:ext cx="1353960" cy="225720"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="43" name="Ink 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0079343-68BE-2AC7-9F01-7F7A827009FB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3298680" y="18686520"/>
+              <a:ext cx="1371600" cy="243360"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>918860</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>187600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>934700</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>53000</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="44" name="Ink 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC10562A-5CA8-6834-E32B-A8EB5AA1CB69}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2912760" y="18882000"/>
+            <a:ext cx="15840" cy="271800"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="44" name="Ink 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC10562A-5CA8-6834-E32B-A8EB5AA1CB69}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2903760" y="18873000"/>
+              <a:ext cx="33480" cy="289440"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -750,23 +2102,19 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:35:01.521"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:55:51.411"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">196 270 24575,'-1'8'0,"0"14"0,1 22 0,0 27 0,0 11 0,0-3 0,0-16 0,0-24 0,0-16 0,0-12 0,0-7 0,0-3 0,1-1 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1399">0 287 24575,'9'0'0,"6"0"0,11-2 0,4 0 0,3 1 0,0 0 0,-2 1 0,2 0 0,-3 2 0,1 4 0,-2 4 0,-2 4 0,-1 4 0,-1 4 0,-1 4 0,-1 3 0,-2 1 0,-3 0 0,-6-6 0,-4-4 0,-5-5 0,-4-2 0,-3 1 0,-5 2 0,-3 4 0,-6 7 0,-5 3 0,-4 2 0,-3 0 0,1-4 0,0-3 0,3-4 0,5-6 0,2-5 0,-1-2 0,-1-2 0,-3-1 0,0-1 0,2-2 0,3 0 0,6-1 0,5-1 0,3-1 0,-2 0 0,4 0 0,-2 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3982">998 508 24575,'-8'0'0,"-7"0"0,-6 0 0,-8 0 0,-3 0 0,-2 0 0,0 0 0,3 2 0,4 3 0,7 3 0,5 3 0,6-1 0,3 2 0,2 3 0,2 4 0,2 5 0,4 8 0,9 6 0,9 0 0,13-2 0,3-9 0,4-7 0,-2-8 0,-8-7 0,-6-5 0,-7-7 0,-3-7 0,0-10 0,1-8 0,-2-2 0,-2 2 0,-4 6 0,-5 7 0,-2 10 0,-3 4 0,-2 3 0,-2-2 0,0-3 0,-1-2 0,0-1 0,2 1 0,0-1 0,2 1 0,1 1 0,0 2 0,1 4 0,8 12 0,7 7 0,11 13 0,5 3 0,2 2 0,-2-3 0,-2-4 0,-6-8 0,-4-7 0,-4-6 0,-1-3 0,3-3 0,3-2 0,2-3 0,-1-4 0,-2-3 0,-4-8 0,-3-19 0,-5-24 0,-3-26 0,-3 37 0,-2-2 0,-1 0 0,-1 1 0,-8-43 0,-5 17 0,-2 19 0,2 16 0,3 15 0,3 10 0,3 9 0,2 6 0,2 2 0,1 3 0,1 3 0,0 4 0,0 8 0,3 16 0,4 19 0,8 27 0,-3-28 0,1 3 0,3 4 0,0 1 0,1-1 0,-1-3 0,15 39 0,-3-24 0,-6-26 0,-3-15 0,-6-15 0,-3-9 0,1-4 0,7 0 0,5-3 0,3-3 0,-1-1 0,-6-1 0,-8 2 0,-5 3 0,-3 1 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4765">1272 419 24575,'17'0'0,"12"0"0,14 0 0,5 0 0,-7 0 0,-12 0 0,-15 0 0,-8 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6699">1788 505 24575,'-5'0'0,"0"1"0,0 2 0,-2 3 0,-1 6 0,-1 5 0,0 5 0,2 3 0,2 3 0,3 1 0,1 3 0,2 0 0,3-1 0,6-3 0,6-7 0,5-7 0,0-7 0,-1-4 0,-4-3 0,-4-2 0,-4-1 0,-2-3 0,-1-3 0,1-3 0,0-3 0,2-5 0,0-5 0,1-6 0,-1-1 0,-1 0 0,-3 6 0,-1 7 0,-2 8 0,-1 6 0,-1 3 0,0 3 0,-1 3 0,0 4 0,0 3 0,-1 2 0,0 1 0,0 1 0,1 0 0,1 1 0,1 0 0,2-1 0,2-1 0,2-2 0,2-3 0,0-2 0,-1-2 0,0 0 0,1 0 0,0 0 0,0 0 0,-2-1 0,-1-1 0,-1-1 0,-2-2 0,0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">347 28 24575,'-5'-2'0,"-5"0"0,-8-3 0,-9-3 0,-9 2 0,-16 1 0,-14 11 0,17 3 0,3 14 0,33 8 0,5 48 0,7-13 0,10 27 0,9-41 0,10-15 0,7-13 0,23-14 0,-15-9 0,7-8 0,-27-2 0,-11-1 0,-7 2 0,-5 0 0,-7-3 0,-11-1 0,-39-10 0,9 9 0,-23-4 0,30 13 0,10 2 0,15 2 0,9 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink10.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -796,7 +2144,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -825,7 +2173,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -855,7 +2203,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink13.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -884,7 +2232,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink14.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -909,6 +2257,609 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">32 6 24575,'10'0'0,"1"0"0,1 0 0,0 0 0,-2 0 0,-2 0 0,-4 0 0,-1-2 0,-1 0 0,-1 0 0,-1 2 0,0 2 0,-1 3 0,0 1 0,0 0 0,-1 3 0,0 1 0,0 4 0,1 2 0,1 4 0,0 1 0,0 1 0,0 1 0,0 1 0,1 1 0,1 1 0,2 1 0,-1 1 0,0-2 0,0 0 0,-1-3 0,-1-3 0,0-1 0,0-3 0,-1-2 0,0-3 0,0-1 0,0-2 0,0 0 0,1-1 0,-1-1 0,1 0 0,-1-1 0,1 1 0,0-1 0,-1 0 0,1-1 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 0 0,0-1 0,-1 0 0,-3-1 0,-1 0 0,-3-1 0,-2 0 0,-2-2 0,-1-1 0,0-1 0,1-1 0,2 3 0,2 0 0,2 2 0,2 0 0,0 0 0,1 0 0,1 0 0,0 0 0,0-1 0,0 0 0,2-2 0,0-2 0,1-3 0,-1 3 0,1 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink15.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:57:22.071"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 18 24575,'29'0'0,"7"0"0,18-2 0,1 0 0,-8-1 0,-11 0 0,-18 1 0,-4 0 0,-4 1 0,-3 0 0,-3 1 0,-2-1 0,-1 0 0,-1 1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink16.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:57:30.552"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">890 54 24575,'-3'8'0,"-7"3"0,-13 7 0,-20 5 0,-9 0 0,-2-4 0,5-8 0,10-8 0,5-8 0,3-7 0,5-7 0,6-7 0,4-1 0,4 3 0,5 3 0,2 5 0,4 5 0,-1 5 0,2 4 0,-1 2 0,-1 3 0,0 1 0,0 1 0,0 1 0,-1 3 0,2 3 0,-1 4 0,-1 5 0,0 2 0,-3 1 0,-3-1 0,-5-2 0,-10-3 0,-11-3 0,-12-5 0,-8-4 0,0-4 0,5-7 0,12-5 0,11-5 0,11-4 0,8-1 0,4 2 0,2 3 0,2 5 0,0 3 0,1 3 0,-1 1 0,2 1 0,0 1 0,-1 1 0,-5 5 0,-1 0 0,-4 6 0,1-1 0,-1 0 0,2-1 0,0-2 0,2-2 0,3-1 0,0-4 0,2-4 0,2-4 0,0-4 0,1-1 0,1 0 0,-1 3 0,0 1 0,0 3 0,0 2 0,0 0 0,0 1 0,0 2 0,2 1 0,-2 0 0,1 0 0,0 2 0,-1 2 0,0 1 0,0 1 0,0 0 0,0 1 0,1-2 0,0 0 0,1-1 0,0-2 0,1 0 0,-1-1 0,0 0 0,-3 0 0,0 0 0,-3-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink17.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:57:36.649"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 24575,'2'9'0,"-1"2"0,-1 3 0,3 3 0,3 1 0,5 0 0,4-3 0,1-5 0,2-3 0,3-5 0,3-4 0,1-6 0,-4-3 0,-5-2 0,-6 0 0,-4 1 0,-2 0 0,-2 0 0,-1 3 0,-1 1 0,0 3 0,0 1 0,0 1 0,0 1 0,0 6 0,0 2 0,0 5 0,1-2 0,0 2 0,1-1 0,0-1 0,0-1 0,2 0 0,3 0 0,7 0 0,7-1 0,6 1 0,3-2 0,-1-2 0,-6-2 0,-6-2 0,-6 0 0,-4-2 0,-2-3 0,-1-2 0,-2-2 0,0 0 0,-2 0 0,0 0 0,0 0 0,0 0 0,0 2 0,0 0 0,0 3 0,0 0 0,1 2 0,-1-1 0,1 1 0,-1 0 0,0 1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink18.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:58:00.353"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">14 5 24575,'0'15'0,"0"1"0,0 1 0,0 2 0,0 1 0,0 6 0,0 4 0,0 1 0,0 5 0,0-7 0,-1-4 0,0-3 0,1-6 0,-1 3 0,0-2 0,0 1 0,0-6 0,0 2 0,0-2 0,1-1 0,0-2 0,0-3 0,0 1 0,0-1 0,0-1 0,0 0 0,0-1 0,0 4 0,0 4 0,-1 4 0,0 2 0,0-2 0,0-4 0,1-3 0,-1-4 0,1-2 0,0 0 0,1-2 0,0 0 0,1-1 0,0 0 0,1 0 0,1-1 0,0 1 0,3-1 0,2-1 0,2 2 0,4-1 0,2 1 0,3 0 0,2 0 0,-1 0 0,0 0 0,-1 0 0,0 0 0,0 0 0,1 0 0,0 0 0,0 0 0,2 0 0,-3 0 0,0 0 0,-3 0 0,-2 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,2 0 0,1 0 0,2-1 0,1 0 0,1 0 0,-1-1 0,-2 2 0,-1-1 0,0 1 0,1 0 0,2 0 0,1 0 0,0 0 0,-2 0 0,-1 0 0,-3 0 0,-2 0 0,-3 0 0,-1 0 0,-2-1 0,-1 1 0,0-2 0,1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,-1-1 0,-1 1 0,0-1 0,-1 0 0,0 1 0,-1 0 0,-1 0 0,-1 0 0,-1-1 0,0 1 0,-1-2 0,0 0 0,0-2 0,0-1 0,0-1 0,0-3 0,0-3 0,0-3 0,0-4 0,-1 1 0,0 0 0,-1 3 0,0 3 0,1 1 0,-1 2 0,1-1 0,0 1 0,0-1 0,0-2 0,0 1 0,-1-2 0,1 1 0,-1 0 0,1 1 0,0 1 0,-1-1 0,1-1 0,-1-1 0,0-3 0,-1 0 0,1 1 0,1 1 0,0 2 0,-1 1 0,2 1 0,-1 2 0,0 0 0,1 3 0,-1 2 0,-1 2 0,1 2 0,-2-1 0,0 1 0,-1 0 0,0 0 0,-2 0 0,-1-1 0,-2-1 0,-3 1 0,-2-1 0,-4-1 0,-2 0 0,-3 1 0,-1-2 0,-1 2 0,1 0 0,2-1 0,1 2 0,1-1 0,1 0 0,0 1 0,0 1 0,0 0 0,-2 0 0,-1 0 0,-2 0 0,-2 0 0,0 0 0,-1 0 0,-1 0 0,-1 0 0,0 0 0,0 0 0,4-1 0,2 0 0,3-1 0,4 0 0,2 0 0,1 0 0,2 0 0,-1 0 0,0 1 0,1-1 0,1 1 0,1 0 0,1-1 0,2 1 0,2-1 0,2 1 0,1 0 0,1 1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink19.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:58:04.180"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 566 24575,'24'17'0,"19"10"0,34 15 0,-24-16 0,5 1 0,9 1 0,5-1 0,10 1 0,3-1 0,8-2 0,2-2-223,-26-8 0,1-1 0,1-1 223,3-1 0,1-1 0,1-1 0,4-1 0,0-1 0,1 0 0,1-2 0,1 0 0,0-1 0,2 0 0,0-1 0,1 0 0,1-1 0,1-1 0,0 0 0,1 0 0,0-1 0,-1-2 0,-3 0 0,-1-2 0,-1 0 0,-2-2 0,-1-2 0,-2 0 0,-7-1 0,-1-2 0,-3 0 0,18-5 0,-4-1 0,-12 1 0,-5 0 0,30-9 0,-31 5 0,-20 5 0,-16 4 669,-14 5-669,-8 2 0,-3 2 0,-3 1 0,-2 0 0,0 0 0,1 0 0,0 0 0,0-1 0,1 0 0,0-2 0,1 0 0,0-1 0,-3-1 0,1 1 0,2 1 0,11-1 0,19-5 0,17-7 0,17-11 0,7-5 0,-3-2 0,2-1 0,-7 4 0,-3 2 0,-2 3 0,-6 6 0,2-1 0,-1 0 0,3-3 0,-5-1 0,-1 0 0,-4-1 0,-6 1 0,-1 0 0,-4 2 0,-3 1 0,-2 2 0,0 0 0,-1 3 0,1-1 0,-2 2 0,0 1 0,-5 1 0,-2 1 0,-3 2 0,-3 0 0,-1 0 0,0 0 0,0-1 0,0 0 0,-3 1 0,-3 3 0,-3 3 0,0 1 0,1 0 0,2-1 0,1 0 0,0-1 0,-2 1 0,-2 2 0,-3 0 0,0 2 0,0-1 0,-1 1 0,-3 0 0,-6 0 0,-9-1 0,-6-1 0,-3-2 0,3 1 0,5 0 0,7 3 0,6 0 0,7 1 0,9 0 0,9 0 0,9 0 0,2 0 0,-3 0 0,-6 0 0,-7 0 0,-5 0 0,-3 0 0,-3 0 0,-1 0 0,-3 1 0,-1 1 0,-1 1 0,-3 3 0,-1 6 0,-2 5 0,0 3 0,0-2 0,2-4 0,2-4 0,1-3 0,1-3 0,1-2 0,0-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:55:52.308"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'12'0'0,"14"0"0,24 0 0,23 0 0,16 0 0,8 0 0,-10 0 0,-13 0 0,-21 0 0,-22 0 0,-14 0 0,-10 0 0,-5 0 0,-2 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink20.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:58:37.828"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">54 6 24575,'35'0'0,"9"0"0,38 0 0,4 0 0,1 0 0,-11 0 0,-15 0 0,-17 0 0,-13 0 0,-8 0 0,-6 0 0,-2-2 0,-3 1 0,-2-1 0,-3 1 0,-2 1 0,-1 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,-1 2 0,-1 6 0,-1 15 0,0 19 0,1 20 0,1 11 0,-1 3 0,-2-6 0,0-15 0,0-16 0,0-16 0,0-11 0,0-6 0,-1-4 0,0-2 0,-1 0 0,-3 0 0,-4 0 0,-9 0 0,-8 0 0,-10 0 0,-4 0 0,-3 0 0,1 0 0,3 1 0,4 0 0,3 2 0,4 2 0,1 0 0,0 1 0,-1 1 0,0-1 0,2 0 0,4-2 0,6 0 0,5-2 0,4-1 0,3-1 0,0 0 0,0 0 0,-2 0 0,-1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,-1 0 0,0-1 0,0 0 0,1 0 0,-2 0 0,0-1 0,-1-1 0,1 1 0,2-1 0,3 0 0,1-1 0,3-2 0,0-2 0,1-2 0,-1-3 0,1-2 0,0-3 0,-2-3 0,0-1 0,-1-1 0,0-1 0,1 0 0,0 1 0,2 1 0,-1 0 0,1 1 0,0 1 0,0 0 0,0 2 0,0 0 0,0-1 0,0 0 0,0 0 0,0 3 0,0 4 0,0 4 0,0 2 0,0 3 0,0 0 0,0 1 0,1 0 0,0 1 0,0 0 0,1 0 0,-1-1 0,-1 0 0,1-1 0,-1 0 0,0 0 0,0 1 0,1 1 0,1-1 0,0 0 0,-1 1 0,0-1 0,0 1 0,1 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,-7 1 0,4 0 0,-5 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink21.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T16:02:14.014"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3 0 24575,'0'13'0,"0"3"0,0 5 0,0 4 0,0 1 0,0 1 0,0-1 0,0 1 0,0 1 0,0 0 0,0-1 0,0 0 0,0 0 0,0 2 0,0 2 0,0 1 0,0 1 0,0-2 0,0-3 0,0-3 0,0-5 0,0-1 0,0-3 0,0-1 0,0-1 0,0-2 0,0-2 0,0-1 0,-1-1 0,1-2 0,-1 1 0,0-1 0,1-1 0,0-1 0,0-2 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink22.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T16:02:30.278"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 25 24575,'0'12'0,"0"5"0,0 5 0,0 3 0,0 1 0,0-3 0,0-1 0,0-2 0,0-1 0,0-4 0,1-5 0,-1-5 0,1-3 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1200">202 243 24575,'-3'0'0,"-2"0"0,2 0 0,0 0 0,1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2634">187 0 24575,'32'0'0,"3"0"0,8 0 0,-1 0 0,-9 0 0,-11 0 0,-11 0 0,-6 1 0,-5 0 0,-1 3 0,-2 2 0,-3 4 0,0 1 0,1 0 0,1-2 0,1-2 0,1-2 0,-1-1 0,-1 1 0,0 1 0,-1 3 0,0 1 0,-1 0 0,2 0 0,0-2 0,0-1 0,2-2 0,0-1 0,1-2 0,0 1 0,-2 2 0,-2 4 0,-1 5 0,-2 5 0,2 0 0,1 0 0,2-5 0,1-7 0,2-3 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4000">507 68 24575,'6'0'0,"7"0"0,7 0 0,4 0 0,-2 0 0,-8 0 0,-8 4 0,-10 7 0,-7 8 0,-4 6 0,-2-1 0,4-6 0,4-7 0,5-5 0,2-5 0,3-3 0,1 0 0,2-1 0,3 2 0,2 1 0,3 0 0,0 2 0,-1 1 0,-4 2 0,-4 2 0,-1 1 0,-2 3 0,-2 3 0,-2 2 0,-3-1 0,-2-3 0,-2-2 0,-1-5 0,-3-2 0,-3-2 0,-4-2 0,-1-2 0,4-1 0,5-1 0,7 3 0,5 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5617">872 133 24575,'-5'0'0,"-1"0"0,-1 0 0,0 0 0,0 0 0,-1 5 0,1 6 0,1 10 0,2 7 0,1 1 0,2-2 0,6-6 0,13-7 0,9-6 0,9-6 0,5-6 0,-6-7 0,-6-3 0,-8 0 0,-11 3 0,-4 4 0,-5 3 0,-2 2 0,-1 1 0,0 1 0,0 0 0,0 0 0,-2 0 0,-3-1 0,-2-2 0,-2-3 0,1-1 0,2 0 0,4 2 0,6 3 0,6 6 0,6 10 0,6 7 0,1 4 0,-4-3 0,-5-5 0,-6-6 0,-3-4 0,-3 0 0,-2 1 0,-5 4 0,-7 2 0,-5 2 0,-3-3 0,2-3-1696,5-3 0,6-4 0,5-2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6767">1093 266 24575,'6'-3'0,"5"1"0,5 2 0,3 0 0,-4 1 0,-4 1 0,-5 4 0,-5 4 0,-2 6 0,-4 4 0,-8 5 0,-5 0 0,-3-3 0,6-5 0,6-7 0,7-6 0,8-3 0,13-6 0,15-4 0,11-2 0,1 1 0,-7 2 0,-12 3 0,-11 2 0,-9 2 0,-4 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="8017">1593 110 24575,'-5'0'0,"1"1"0,1 3 0,2 6 0,0 9 0,0 5 0,0 3 0,0-3 0,9-6 0,10-4 0,11-6 0,10-3 0,-2-5 0,-8-4 0,-9-4 0,-10-4 0,-5 0 0,-4-1 0,-1 4 0,0 4 0,0 3 0,0 9 0,0 2 0,0 7 0,0-1 0,0 0 0,0 0 0,-1 1 0,-3-1 0,-4 1 0,-6 0 0,-4 0 0,-3-2 0,-2-3 0,-1-5 0,-2-3 0,12-2 0,2-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="9316">1550 141 24575,'0'-4'0,"0"-1"0,1 0 0,2-2 0,5 0 0,6-1 0,8-1 0,5 1 0,1 2 0,-3 2 0,-7 3 0,-5 2 0,-1 6 0,-1 5 0,0 4 0,-1 1 0,-3-3 0,-3-5 0,-2-2 0,-1-2 0,-1-2 0,0 0 0,0-2 0,0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10067">1911 66 24575,'7'-1'0,"10"6"0,14 9 0,8 8 0,1 4 0,-9-4 0,-10-7 0,-11-8 0,-6-4 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="10949">2111 19 24575,'-9'15'0,"0"1"0,0-2 0,2-4 0,4-4 0,0-1 0,-2 2 0,-4 5 0,-4 3 0,-1 1 0,3-3 0,2-3 0,4-4 0,4-4 0,0 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink23.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T16:02:45.644"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 363 24575,'0'9'0,"0"12"0,0 18 0,0 12 0,0 3 0,0-9 0,0-17 0,0-14 0,0-10 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1066">203 444 24575,'8'10'0,"4"5"0,5 3 0,4 2 0,4-2 0,3-6 0,5-5 0,1-4 0,-1-8 0,-2-10 0,-5-8 0,-7-4 0,-6 1 0,-7 1 0,-5 3 0,-11-3 0,-14 0 0,-12 2 0,-11 4 0,-3 7 0,2 5 0,7 4 0,9 3 0,12 0 0,10 0 0,5 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2233">640 1 24575,'-13'0'0,"-9"0"0,-6 0 0,0 0 0,7 0 0,11 4 0,5 5 0,5 8 0,2 6 0,3 2 0,1-5 0,1-6 0,-1-6 0,0-5 0,4-2 0,7-4 0,8-3 0,6-2 0,1 0 0,10 9 0,-14 8 0,2 8 0,-18 3 0,-6-3 0,-5-5 0,-12-3 0,-16 0 0,-13 0 0,-8-2 0,5-2 0,13-3 0,14-2 0,9 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink24.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T16:03:04.759"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#FF0066"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'0'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink25.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T16:03:15.476"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#FF0066"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">518 36 24575,'-27'0'0,"-5"0"0,-10 0 0,-5 0 0,-4 3 0,0 5 0,5 4 0,3 6 0,4 8 0,2 8 0,4 9 0,4 6 0,8 1 0,8-3 0,7-6 0,7-7 0,13-7 0,18-5 0,27-6 0,24-4 0,9-6 0,-7-4 0,-21-3 0,-26-4 0,-18-6 0,-15-6 0,-15-5 0,-12-3 0,-16 0 0,-10 4 0,-2 6 0,1 6 0,11 6 0,9 2 0,11 0 0,9 1 0,5 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="515">735 376 24575,'0'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1482">878 145 24575,'23'0'0,"6"0"0,9 0 0,-2 0 0,-11 0 0,-11 1 0,-9 4 0,-4 13 0,-6 19 0,-5 19 0,-1 11 0,0-1 0,4-10 0,3-16 0,2-13 0,1-15 0,1-7 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2616">1305 224 24575,'9'-6'0,"11"2"0,14 2 0,8 1 0,3 5 0,-8 5 0,-10 13 0,-11 13 0,-12 14 0,-13 12 0,-18 4 0,-12-5 0,-10-10 0,1-17 0,6-14 0,4-10 0,10-14 0,8-8 0,9-6 0,7-2 0,8 0 0,13 1 0,14 4 0,14 4 0,7 6 0,3 7 0,2 6 0,-4 5 0,-5 2 0,-9-2-1696,-10-4 0,-14-4 0,-6-2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3332">1884 151 24575,'26'20'0,"5"3"0,7 6 0,-1-1 0,-9-7 0,-8-7 0,-8-6 0,-3-2-1696,-2-2 0,-3-1 0,-2-2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4132">2119 141 24575,'-8'4'0,"1"1"0,2 4 0,2-1 0,2-1 0,1-1 0,-1 2 0,-4 5 0,-4 4 0,-6 4 0,-4 2 0,-1 0 0,2-4 0,4-4-1696,5-5 0,5-5 0,2-3 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4815">2495 239 24575,'-2'31'0,"1"10"0,1 5 0,0-4 0,0-14 0,0-15 0,0-6 0,0-6 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5849">2780 170 24575,'-3'13'0,"1"6"0,7 10 0,12 5 0,15 2 0,13-6 0,6-11 0,-2-10 0,-6-9 0,-7-10 0,-10-10 0,-8-13 0,-9-11 0,-11-5 0,-13 1 0,-10 6 0,-9 10 0,-5 8 0,1 10 0,2 8 0,6 4 0,6 4 0,6 2 0,6 2 0,3 2 0,3 0 0,3-4 0,2-2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6599">3188 62 24575,'20'0'0,"7"0"0,2 0 0,-2 0 0,-14 0 0,-6 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="7765">3461 0 24575,'0'9'0,"0"3"0,0 2 0,1-3 0,8-3 0,13-6 0,19-2 0,13 2 0,0 2 0,-9 0 0,-17 0 0,-13-3 0,-10-4 0,-5-3 0,-2-1 0,-1 4 0,1 14 0,2 18 0,2 16 0,3 9 0,2-5 0,0-11 0,-3-12 0,-1-12 0,-1-7 0,-2-5 0,1-2 0,1 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink26.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T16:05:00.768"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#FF0066"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">43 0 24575,'-1'11'0,"0"9"0,-1 8 0,-3 9 0,-1 4 0,-2 0 0,2 0 0,2-1 0,1 2 0,2 0 0,0-1 0,0-4 0,0-3 0,0-3 0,0-3 0,0-3 0,1-4 0,0-5 0,0-6 0,0-3 0,0-2 0,0-2 0,0 2 0,0 5 0,0 9 0,0 7 0,0 3 0,0-2 0,0-9 0,0-7 0,1-5 0,-1-4 0,0-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:56:05.407"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 426 24575,'0'24'0,"0"20"0,0 24 0,0 12 0,0-3 0,0-19 0,0-24 0,0-17 0,0-11 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1366">408 523 24575,'-7'-2'0,"-2"1"0,-2 3 0,-3 4 0,1 3 0,1 5 0,4 2 0,2 2 0,2 4 0,2 1 0,1 3 0,0-1 0,3-2 0,0-4 0,4-5 0,3-4 0,7-3 0,7 0 0,6-2 0,3-3 0,0 0 0,-3-2 0,-7-1 0,-5 0 0,-6-3 0,-5-2 0,-3-2 0,-2 0 0,-1-1 0,0 0 0,-1-1 0,-3 1 0,-6 2 0,-7 2 0,-29 1 0,4 2 0,-14 1 0,21 1 0,12 0 0,13 0 0,6 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2183">560 165 24575,'30'0'0,"-7"0"0,13 0 0,-19 0 0,-8 0 0,-6 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3483">932 1 24575,'0'13'0,"0"5"0,0 10 0,0 1 0,0-6 0,0-7 0,0-7 0,0-4 0,0-1 0,0 0 0,0 2 0,0 2 0,0 1 0,0 1 0,1 0 0,0-2 0,-1 0 0,0-1 0,0 0 0,0-3 0,0-1 0,0-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:56:03.041"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">300 31 24575,'-6'0'0,"-4"0"0,-8 0 0,-5 0 0,-9 0 0,-2 0 0,2 2 0,0 6 0,3 12 0,1 13 0,4 11 0,4 34 0,11-13 0,7 20 0,17-30 0,12-8 0,10-16 0,8-10 0,5-10 0,35-26 0,-19-6 0,14-15 0,-41 7 0,-16 7 0,-13 6 0,-12 3 0,-17 1 0,-22 0 0,-53-2 0,19 7 0,-22 2 0,52 5 0,16 0 0,18 0 0,7 0 0,3 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="733">793 9 24575,'29'10'0,"16"14"0,14 11 0,2 6 0,-13-6 0,-17-12 0,-17-12 0,-7-6 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1583">1064 0 24575,'-6'9'0,"-6"8"0,-4 9 0,-7 5 0,0 0 0,4-4 0,4-6 0,5-7 0,5-5 0,2-5 0,1-2 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:56:01.158"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">5 1 24575,'-4'1'0,"23"0"0,18 0 0,26-1 0,10 0 0,-5 0 0,-15 0 0,-16 0 0,-18 0 0,-11 0 0,-6 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="666">132 157 24575,'10'0'0,"18"0"0,25 0 0,16 0 0,3 0 0,-17 0 0,-27 0 0,-13 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:55:56.059"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">255 39 24575,'0'12'0,"0"7"0,0 9 0,0 6 0,0-2 0,0-7 0,0-7 0,0-7 0,0-5 0,1-3 0,2-2 0,1-1 0,1 0 0,1 0 0,3-1 0,3-2 0,5-1 0,4-3 0,2-1 0,-2 1 0,-3-1 0,-5 3 0,-5 1 0,-3 2 0,-2 0 0,-2 2 0,-1-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="900">1 100 24575,'0'13'0,"0"9"0,0 8 0,0 5 0,0 0 0,0-4 0,0-6 0,0-11 0,0-7 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1966">9 219 24575,'-1'43'0,"0"13"0,1 15 0,0-1 0,0-14 0,0-19 0,0-14 0,0-14 0,0-6 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4300">267 145 24575,'0'-16'0,"0"-3"0,3-3 0,5-1 0,6 2 0,7 5 0,6 4 0,5 4 0,1 3 0,-3 3 0,-5 2 0,-6 0 0,-7 0 0,-3 0 0,-6 0 0,-5 0 0,-5 0 0,-6 0 0,-4 0 0,-3 0 0,0 0 0,3 0 0,2 2 0,3 3 0,3 4 0,0 5 0,2 4 0,-3 5 0,-1 5 0,-1 2 0,1-1 0,2-4 0,2-5 0,3-3 0,1-2 0,2-2 0,0-1 0,1-1 0,0 1 0,0 0 0,0 0 0,0 2 0,1 0 0,2 1 0,4 0 0,3-1 0,4-2 0,3-2 0,1-3 0,3-2 0,0-3 0,2-2 0,3-3 0,4-7 0,2-6 0,1-5 0,-3-2 0,-5 1 0,-6 1 0,-8 3 0,-6 3 0,-4 3 0,-4 2 0,-6 0 0,-6-3 0,-7-2 0,-3-1 0,1-1 0,3 3 0,4 4 0,4 5 0,2 2 0,1 3 0,1 0 0,-2 0 0,-2 0 0,-2 0 0,-1 2 0,1 1 0,4 1 0,5-1 0,3 0 0,2-1 0,0 1 0,1-1 0,0-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:56:23.339"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">197 519 24575,'0'-19'0,"0"0"0,-1-2 0,-5 3 0,-6 7 0,-9 5 0,-9 3 0,-2 2 0,2 1 0,7 1 0,8 3 0,5 3 0,5 7 0,0 5 0,1 7 0,2 4 0,1 3 0,1-2 0,1-7 0,3-7 0,4-7 0,4-5 0,5-1 0,6-2 0,3-1 0,0-2 0,-1-3 0,-6-4 0,-4-2 0,-4-2 0,-4-1 0,-3 0 0,0 0 0,-3-1 0,0 2 0,0 4 0,-1 2 0,0 6 0,0 5 0,0 7 0,3 11 0,5 12 0,7 9 0,6 5 0,3-2 0,0-9 0,-4-12 0,-6-12 0,-6-9 0,-3-4 0,-2-3 0,0-2 0,-1 1 0,-1 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="833">700 361 24575,'27'26'0,"6"5"0,6 6 0,0-1 0,-10-11 0,-9-8 0,-8-8 0,-3-3 0,6 4 0,15 11 0,10 9 0,8 4 0,-5-4 0,-13-10 0,-13-7 0,-11-10 0,-5-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1567">1089 515 24575,'-5'1'0,"-3"8"0,-7 11 0,-4 10 0,-2 5 0,1-1 0,3-7 0,6-8 0,5-10 0,5-5 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2868">1555 295 24575,'0'20'0,"0"8"0,0 4 0,0 3 0,0-3 0,0-9 0,0-6 0,0-7 0,3-5 0,6 0 0,13 0 0,11 0 0,11-2 0,4-1 0,-3-2 0,-8-1 0,-9-2 0,-12-3 0,-6-4 0,-6-1 0,-3 0 0,-1 0 0,-3-4 0,0 6 0,-4-5 0,0 7 0,-6 0 0,-1 2 0,-7-1 0,-2 0 0,-6-1 0,-18 0 0,14 4 0,-5 0 0,24 3 0,7 1 0,5-1 0,0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3616">1828 114 24575,'23'0'0,"3"0"0,2 0 0,-2 0 0,-4 0 0,-9 0 0,-6 0 0,-4 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4783">2380 1 24575,'-4'0'0,"-3"0"0,-1 0 0,-4 0 0,-2 3 0,-1 1 0,1 3 0,3 3 0,3 1 0,3 2 0,3 3 0,1 3 0,1 3 0,1 0 0,3 0 0,2-4 0,4-5 0,5-5 0,4-2 0,4-1 0,4-2 0,-1-1 0,-2 0 0,-6-1 0,-5 0 0,-7-1 0,-3 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-06T15:56:16.709"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">269 1 24575,'-10'0'0,"-7"0"0,-8 0 0,-8 0 0,-2 0 0,0 0 0,5 0 0,-1 9 0,11 4 0,1 11 0,10 3 0,5 3 0,5 6 0,31 16 0,-6-22 0,28 5 0,-16-34 0,16-20 0,-13-2 0,5-13 0,-23 8 0,-8 5 0,-8 7 0,-4 3 0,-1 5 0,-2 1 0,0 3 0,0 1 0,0 5 0,5 24 0,5 4 0,8 22 0,6-8 0,3-2 0,-2-12 0,-1-10 0,-2-10 0,-3-7 0,-3-5 0,-4-3 0,-8 1 0,-2-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="697">30 540 24575,'19'0'0,"27"0"0,48 0 0,-26 0 0,4 0 0,7 0 0,1 0 0,-4 0 0,-4 0 0,-14 0 0,-5 0 0,16 0 0,-32 0 0,-23 0 0,-9 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1947">456 878 24575,'-1'19'0,"0"5"0,1 8 0,0 3 0,0 2 0,0-4 0,0-1 0,1-6 0,3-5 0,4-4 0,8-5 0,17-3 0,19-1 0,16-5 0,5-7 0,-8-9 0,-17-8 0,-15-4 0,-16 1 0,-11 1 0,-5 5 0,-6 2 0,-8 2 0,-11 3 0,-10 1 0,-8 3 0,0 2 0,5 3 0,8 1 0,11 1 0,8 1 0,5 0 0,2 1 0,2 0 0,1-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3631">915 708 24575,'2'-4'0,"1"1"0,2 2 0,0 2 0,1 0 0,-1 3 0,0 2 0,0 0 0,-3 1 0,0-1 0,-1-2 0,-1-2 0,-3-8 0,-2 0 0,-2-5 0,-1 5 0,0 2 0,0 1 0,0 1 0,0 1 0,3 1 0,0 0 0,0 1 0,1 1 0,0 2 0,1 2 0,2 2 0,0 1 0,1 2 0,0 1 0,0 2 0,2-1 0,1-2 0,1-2 0,1-3 0,1-3 0,1-3 0,2 0 0,1 0 0,0-1 0,-1-1 0,-2 1 0,-4 0 0,-1 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4414">1282 299 24575,'34'0'0,"8"0"0,11 0 0,-3 0 0,-18 0 0,-15 0 0,-9 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5063">1228 424 24575,'27'0'0,"17"0"0,21 0 0,8 0 0,-7 0 0,-15 0 0,-21 0 0,-14 0 0,-9 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-04T16:35:01.521"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">196 270 24575,'-1'8'0,"0"14"0,1 22 0,0 27 0,0 11 0,0-3 0,0-16 0,0-24 0,0-16 0,0-12 0,0-7 0,0-3 0,1-1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1399">0 287 24575,'9'0'0,"6"0"0,11-2 0,4 0 0,3 1 0,0 0 0,-2 1 0,2 0 0,-3 2 0,1 4 0,-2 4 0,-2 4 0,-1 4 0,-1 4 0,-1 4 0,-1 3 0,-2 1 0,-3 0 0,-6-6 0,-4-4 0,-5-5 0,-4-2 0,-3 1 0,-5 2 0,-3 4 0,-6 7 0,-5 3 0,-4 2 0,-3 0 0,1-4 0,0-3 0,3-4 0,5-6 0,2-5 0,-1-2 0,-1-2 0,-3-1 0,0-1 0,2-2 0,3 0 0,6-1 0,5-1 0,3-1 0,-2 0 0,4 0 0,-2 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3982">998 508 24575,'-8'0'0,"-7"0"0,-6 0 0,-8 0 0,-3 0 0,-2 0 0,0 0 0,3 2 0,4 3 0,7 3 0,5 3 0,6-1 0,3 2 0,2 3 0,2 4 0,2 5 0,4 8 0,9 6 0,9 0 0,13-2 0,3-9 0,4-7 0,-2-8 0,-8-7 0,-6-5 0,-7-7 0,-3-7 0,0-10 0,1-8 0,-2-2 0,-2 2 0,-4 6 0,-5 7 0,-2 10 0,-3 4 0,-2 3 0,-2-2 0,0-3 0,-1-2 0,0-1 0,2 1 0,0-1 0,2 1 0,1 1 0,0 2 0,1 4 0,8 12 0,7 7 0,11 13 0,5 3 0,2 2 0,-2-3 0,-2-4 0,-6-8 0,-4-7 0,-4-6 0,-1-3 0,3-3 0,3-2 0,2-3 0,-1-4 0,-2-3 0,-4-8 0,-3-19 0,-5-24 0,-3-26 0,-3 37 0,-2-2 0,-1 0 0,-1 1 0,-8-43 0,-5 17 0,-2 19 0,2 16 0,3 15 0,3 10 0,3 9 0,2 6 0,2 2 0,1 3 0,1 3 0,0 4 0,0 8 0,3 16 0,4 19 0,8 27 0,-3-28 0,1 3 0,3 4 0,0 1 0,1-1 0,-1-3 0,15 39 0,-3-24 0,-6-26 0,-3-15 0,-6-15 0,-3-9 0,1-4 0,7 0 0,5-3 0,3-3 0,-1-1 0,-6-1 0,-8 2 0,-5 3 0,-3 1 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4765">1272 419 24575,'17'0'0,"12"0"0,14 0 0,5 0 0,-7 0 0,-12 0 0,-15 0 0,-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="6699">1788 505 24575,'-5'0'0,"0"1"0,0 2 0,-2 3 0,-1 6 0,-1 5 0,0 5 0,2 3 0,2 3 0,3 1 0,1 3 0,2 0 0,3-1 0,6-3 0,6-7 0,5-7 0,0-7 0,-1-4 0,-4-3 0,-4-2 0,-4-1 0,-2-3 0,-1-3 0,1-3 0,0-3 0,2-5 0,0-5 0,1-6 0,-1-1 0,-1 0 0,-3 6 0,-1 7 0,-2 8 0,-1 6 0,-1 3 0,0 3 0,-1 3 0,0 4 0,0 3 0,-1 2 0,0 1 0,0 1 0,1 0 0,1 1 0,1 0 0,2-1 0,2-1 0,2-2 0,2-3 0,0-2 0,-1-2 0,0 0 0,1 0 0,0 0 0,0 0 0,-2-1 0,-1-1 0,-1-1 0,-2-2 0,0 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1229,21 +3180,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF41FB1-49DC-3A40-AFA3-57CD558B7C2A}">
-  <dimension ref="A2:G40"/>
+  <dimension ref="A2:G48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -1261,13 +3212,13 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
@@ -1283,7 +3234,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17" t="s">
@@ -1299,11 +3250,11 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
@@ -1316,11 +3267,11 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
@@ -1332,19 +3283,40 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="D48" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1352,12 +3324,13 @@
     <mergeCell ref="B2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2D4421-5602-7847-825B-E5B2B05208AD}">
-  <dimension ref="A2:E76"/>
+  <dimension ref="A2:E105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -1365,14 +3338,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
@@ -1380,36 +3353,36 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>646464</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>377373</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>38383.938999999998</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>8383.8330000000005</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>8383.3999000000003</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
@@ -1420,63 +3393,63 @@
       <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+      <c r="B25" s="4">
         <v>646464</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>646464</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="6">
+      <c r="B26" s="4">
         <v>377373</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="8">
+      <c r="C26" s="7"/>
+      <c r="D26" s="6">
         <v>377373</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B27" s="6">
+      <c r="B27" s="4">
         <v>0</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="6">
         <v>38383.938999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+      <c r="B28" s="4">
         <v>8383.8330000000005</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+      <c r="B29" s="4">
         <v>-8383.3999000000003</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>-8383.3999000000003</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="8">
         <v>46238</v>
       </c>
     </row>
@@ -1484,25 +3457,25 @@
       <c r="B34" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="9">
         <v>46238</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="10">
+      <c r="B36" s="8">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
-      </c>
-      <c r="C36" s="4">
+        <v>46240</v>
+      </c>
+      <c r="C36" s="2">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1510,7 +3483,7 @@
       <c r="B39">
         <v>2</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="8">
         <v>2</v>
       </c>
     </row>
@@ -1518,7 +3491,7 @@
       <c r="B40">
         <v>3</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="8">
         <v>3</v>
       </c>
     </row>
@@ -1526,7 +3499,7 @@
       <c r="B41">
         <v>4</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="8">
         <v>4</v>
       </c>
     </row>
@@ -1534,29 +3507,29 @@
       <c r="B43">
         <v>36728</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="8">
         <v>36728</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="12">
+      <c r="B44" s="10">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
-      </c>
-      <c r="C44" s="10">
+        <v>46240</v>
+      </c>
+      <c r="C44" s="8">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="2"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="2"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="1"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
@@ -1587,7 +3560,7 @@
       <c r="B57">
         <v>0.5</v>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="13">
         <v>0.5</v>
       </c>
     </row>
@@ -1595,7 +3568,7 @@
       <c r="B58">
         <v>0.75</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="13">
         <v>0.75</v>
       </c>
     </row>
@@ -1603,7 +3576,7 @@
       <c r="B59">
         <v>0.46929999999999999</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="13">
         <v>0.46930555555555553</v>
       </c>
     </row>
@@ -1613,28 +3586,28 @@
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B64" s="5">
+      <c r="B64" s="3">
         <v>46238.75</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B66" s="10"/>
+      <c r="B66" s="8"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B67" s="16">
+      <c r="B67" s="14">
         <f ca="1">NOW()</f>
-        <v>46238.960435532405</v>
-      </c>
-      <c r="C67" s="4">
+        <v>46240.907507870368</v>
+      </c>
+      <c r="C67" s="2">
         <f ca="1">NOW()</f>
-        <v>46238.960435532405</v>
+        <v>46240.907507870368</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
@@ -1647,7 +3620,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C74" s="10"/>
+      <c r="C74" s="8"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
@@ -1657,6 +3630,127 @@
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B84" s="2"/>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>0.05</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" s="18">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B88">
+        <v>392492432839942</v>
+      </c>
+      <c r="D88" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B90" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B92">
+        <v>173929</v>
+      </c>
+      <c r="C92">
+        <v>173929</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B93">
+        <v>6.7199999999999996E-4</v>
+      </c>
+      <c r="C93">
+        <v>6.7199999999999996E-4</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B94">
+        <v>2883</v>
+      </c>
+      <c r="C94">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B99" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101">
+        <v>0.54300000000000004</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B102" s="16">
+        <v>0.54300000000000004</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B103">
+        <v>0.25</v>
+      </c>
+      <c r="C103" s="19">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B104">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="C104" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B105">
+        <v>0.25</v>
+      </c>
+      <c r="C105" s="20">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1791,11 +3885,11 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
